--- a/artfynd/A 66887-2021 artfynd.xlsx
+++ b/artfynd/A 66887-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934430</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934438</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934432</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934433</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934434</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934436</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934439</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934431</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066341</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,8 +1807,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934435</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 66887-2021 artfynd.xlsx
+++ b/artfynd/A 66887-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134934430</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>134934438</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>134934432</v>
       </c>
       <c r="B4" t="n">
-        <v>58519</v>
+        <v>58524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>134934433</v>
       </c>
       <c r="B5" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>134934434</v>
       </c>
       <c r="B6" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>134934436</v>
       </c>
       <c r="B7" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>134934439</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>134934431</v>
       </c>
       <c r="B9" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>135066341</v>
       </c>
       <c r="B10" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>134934435</v>
       </c>
       <c r="B11" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 66887-2021 artfynd.xlsx
+++ b/artfynd/A 66887-2021 artfynd.xlsx
@@ -1594,7 +1594,7 @@
         <v>135066341</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
